--- a/StructureDefinition-openimis-enrolment-officer-practitioner.xlsx
+++ b/StructureDefinition-openimis-enrolment-officer-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10760,7 +10760,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>22</v>
@@ -14861,7 +14861,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>22</v>
@@ -16148,7 +16148,7 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>22</v>
@@ -16495,7 +16495,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>22</v>
@@ -16610,7 +16610,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>22</v>
@@ -16844,7 +16844,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>22</v>
@@ -17893,7 +17893,7 @@
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-enrolment-officer-practitioner.xlsx
+++ b/StructureDefinition-openimis-enrolment-officer-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-enrolment-officer-practitioner.xlsx
+++ b/StructureDefinition-openimis-enrolment-officer-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
